--- a/tools/excel_export/excel/attributes.xlsx
+++ b/tools/excel_export/excel/attributes.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -103,10 +103,7 @@
     <t>伤害输出倍率</t>
   </si>
   <si>
-    <t>物理受伤倍率</t>
-  </si>
-  <si>
-    <t>魔法受伤倍率</t>
+    <t>受伤减免倍率</t>
   </si>
   <si>
     <t>暴击率</t>
@@ -119,6 +116,27 @@
   </si>
   <si>
     <t>攻击距离</t>
+  </si>
+  <si>
+    <t>金币获取</t>
+  </si>
+  <si>
+    <t>经验获取</t>
+  </si>
+  <si>
+    <t>冷却缩减</t>
+  </si>
+  <si>
+    <t>抽卡折扣</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>攻击回复</t>
+  </si>
+  <si>
+    <t>攻击回蓝</t>
   </si>
 </sst>
 </file>
@@ -558,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -704,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,7 +762,7 @@
         <v>-20</v>
       </c>
       <c r="F9" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -784,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4">
-        <v>95</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -844,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="4">
-        <v>1000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,75 +879,75 @@
         <v>100</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15" s="4">
-        <v>1000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
         <v>100</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="4">
-        <v>100</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E18" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>35</v>
@@ -938,13 +956,133 @@
         <v>17</v>
       </c>
       <c r="D19" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
         <v>50</v>
       </c>
-      <c r="F19" s="4">
-        <v>2000</v>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>25</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>27</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <v>9999</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel_export/excel/attributes.xlsx
+++ b/tools/excel_export/excel/attributes.xlsx
@@ -1,12 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\cocos\jihe_defence\tools\excel_export\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="27165" windowHeight="10845"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="attributes" state="visible" r:id="rId4"/>
+    <sheet name="attributes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -142,38 +163,199 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FF404040"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-    </font>
-    <font>
-      <color rgb="FF404040"/>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,20 +365,209 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -219,9 +590,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -238,17 +851,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -570,14 +1227,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -585,7 +1242,7 @@
     <col min="4" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +1262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -625,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -645,7 +1302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" ht="16.5" spans="1:6">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -662,10 +1319,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>999999999999</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:6">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -682,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:6">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -702,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>999999999999</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -725,7 +1382,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" ht="16.5" spans="1:6">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -745,7 +1402,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" ht="16.5" spans="1:6">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -765,7 +1422,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.5" spans="1:6">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -785,7 +1442,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.5" spans="1:6">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -805,7 +1462,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" ht="16.5" spans="1:6">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -822,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>999999999999</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:6">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -842,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="4">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>999999999999</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:6">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -865,7 +1522,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.5" spans="1:6">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -885,7 +1542,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" ht="16.5" spans="1:6">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -905,7 +1562,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" ht="16.5" spans="1:6">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -925,7 +1582,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" ht="16.5" spans="1:6">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -945,7 +1602,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" ht="16.5" spans="1:6">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -965,7 +1622,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" ht="16.5" spans="1:6">
       <c r="A20" s="4">
         <v>22</v>
       </c>
@@ -985,7 +1642,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" ht="16.5" spans="1:6">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -1005,7 +1662,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" ht="16.5" spans="1:6">
       <c r="A22" s="4">
         <v>24</v>
       </c>
@@ -1022,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:6">
       <c r="A23" s="4">
         <v>25</v>
       </c>
@@ -1045,7 +1702,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" ht="16.5" spans="1:6">
       <c r="A24" s="4">
         <v>26</v>
       </c>
@@ -1065,7 +1722,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" ht="16.5" spans="1:6">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -1087,11 +1744,12 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：add / percent / multiply / complement / best" sqref="C4:C160">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：add / percent / multiply / complement / best" sqref="C4:C9 C10:C160">
       <formula1>"add,percent,multiply,complement,best"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>